--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3231-464-CM25</t>
+          <t>840405-15-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.110.700-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE RIO CLARO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>14164.33</v>
+        <v>10652.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2827-927-CM25</t>
+          <t>3756-627-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4437.51</v>
+        <v>11584.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3696-477-CM25</t>
+          <t>3231-464-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3171.77</v>
+        <v>14164.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3876-242-CM25</t>
+          <t>2827-927-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>954.38</v>
+        <v>4437.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2445-1534-CM26</t>
+          <t>3696-477-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7076.45</v>
+        <v>3171.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2436-10-CM26</t>
+          <t>3876-242-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>36561.68</v>
+        <v>954.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1709-694-CM25</t>
+          <t>2445-1534-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.120.400-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CAUQUENES</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>16559.9</v>
+        <v>7076.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2292-6077-CM26</t>
+          <t>2436-10-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2579.68</v>
+        <v>36561.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4401-124-CM26</t>
+          <t>1709-694-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.120.400-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE CAUQUENES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2875.98</v>
+        <v>16559.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3876-16-CM26</t>
+          <t>2292-6077-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2863.21</v>
+        <v>2579.68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3469-112-CM26</t>
+          <t>4401-124-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>28821.15</v>
+        <v>2875.98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2291-351-CM26</t>
+          <t>3876-16-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4649.57</v>
+        <v>2863.21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4085-152-CM26</t>
+          <t>3469-112-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12404.04</v>
+        <v>28821.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1079566-96-CM26</t>
+          <t>2291-351-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1056.72</v>
+        <v>4649.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3470-18-CM26</t>
+          <t>4085-152-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2200.86</v>
+        <v>12404.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4085-191-CM26</t>
+          <t>1079566-96-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>SECCIÓN COMPRAS VII ZONA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10353</v>
+        <v>1056.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3756-258-CM26</t>
+          <t>3470-18-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>11614.4</v>
+        <v>2200.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3874-67-CM26</t>
+          <t>4085-191-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2523.99</v>
+        <v>10353</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4134-274-CM26</t>
+          <t>3756-258-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>22175.65</v>
+        <v>11614.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>840405-21-CM26</t>
+          <t>3874-67-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.110.700-0</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO CLARO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10644.31</v>
+        <v>2523.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2294-724-CM26</t>
+          <t>4134-274-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I. Municipalidad Sagrada Familia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2747.47</v>
+        <v>22175.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5056-1527-CM26</t>
+          <t>840405-21-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>69.110.700-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>I MUNICIPALIDAD DE RIO CLARO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,32 +1835,28 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>221607.75</v>
+        <v>10644.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2292-6734-CM26</t>
+          <t>2294-724-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1870,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1900,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>76195.53</v>
+        <v>2747.47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2445-2218-CM26</t>
+          <t>5056-1527-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1936,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,28 +1957,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4860.09</v>
+        <v>221607.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3442-276-CM26</t>
+          <t>2292-6734-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1997,22 +1997,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>26610.78</v>
+        <v>76195.53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2318-537-CM26</t>
+          <t>2445-2218-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>40280.79</v>
+        <v>4860.09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3251-468-CM26</t>
+          <t>3442-276-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,22 +2119,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,6 +2159,128 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
+        <v>26610.78</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2318-537-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.130.100-1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>40280.79</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3251-468-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.252.700-3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
         <v>13733.65</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Maule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>840405-15-CM25</t>
+          <t>2436-31-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.110.700-0</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO CLARO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10652.88</v>
+        <v>31754.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3756-627-CM25</t>
+          <t>1709-20-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.120.400-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE CAUQUENES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11584.65</v>
+        <v>21638.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3231-464-CM25</t>
+          <t>4401-66-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14164.33</v>
+        <v>2749.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2827-927-CM25</t>
+          <t>4401-64-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4437.51</v>
+        <v>233.14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3696-477-CM25</t>
+          <t>2292-196-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3171.77</v>
+        <v>2115.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3876-242-CM25</t>
+          <t>2292-209-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>954.38</v>
+        <v>2355.81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2445-1534-CM26</t>
+          <t>840405-15-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.700-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE RIO CLARO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7076.45</v>
+        <v>10652.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2436-10-CM26</t>
+          <t>906973-9-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>36561.68</v>
+        <v>26632.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1709-694-CM25</t>
+          <t>2292-401-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.120.400-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CAUQUENES</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>16559.9</v>
+        <v>856.5599999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2292-6077-CM26</t>
+          <t>3756-273-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2579.68</v>
+        <v>12138</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4401-124-CM26</t>
+          <t>2294-658-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2875.98</v>
+        <v>2326.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3876-16-CM26</t>
+          <t>2292-708-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2863.21</v>
+        <v>3595.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3469-112-CM26</t>
+          <t>2292-788-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>28821.15</v>
+        <v>35509.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2291-351-CM26</t>
+          <t>1142-220-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.511.070-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4649.57</v>
+        <v>6556.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4085-152-CM26</t>
+          <t>2318-690-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>12404.04</v>
+        <v>2463.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1079566-96-CM26</t>
+          <t>3876-125-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1056.72</v>
+        <v>3748.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3470-18-CM26</t>
+          <t>3300-124-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2200.86</v>
+        <v>6214.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4085-191-CM26</t>
+          <t>3880-423-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10353</v>
+        <v>26632.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3756-258-CM26</t>
+          <t>3756-627-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>11614.4</v>
+        <v>11584.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3874-67-CM26</t>
+          <t>2292-9091-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2523.99</v>
+        <v>2537.56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4134-274-CM26</t>
+          <t>2445-3581-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>22175.65</v>
+        <v>6247.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>840405-21-CM26</t>
+          <t>3231-464-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.110.700-0</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO CLARO</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>10644.31</v>
+        <v>14164.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2294-724-CM26</t>
+          <t>2827-927-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2747.47</v>
+        <v>4437.51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5056-1527-CM26</t>
+          <t>3696-477-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,32 +1957,28 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>221607.75</v>
+        <v>3171.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2292-6734-CM26</t>
+          <t>3876-242-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>76195.53</v>
+        <v>954.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2445-2218-CM26</t>
+          <t>2445-1534-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2083,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4860.09</v>
+        <v>7076.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3442-276-CM26</t>
+          <t>2436-10-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2159,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>26610.78</v>
+        <v>36561.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2318-537-CM26</t>
+          <t>1709-694-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>69.120.400-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE CAUQUENES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>40280.79</v>
+        <v>16559.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3251-468-CM26</t>
+          <t>2292-6077-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2281,7 +2277,1353 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
+        <v>2579.68</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4401-124-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>2875.98</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3876-16-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.100.400-7</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>2863.21</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3469-112-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.120.300-k</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>28821.15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2291-351-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>4649.57</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4085-152-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.130.600-3</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>12404.04</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1079566-96-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.979.370-6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS VII ZONA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1056.72</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3470-18-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.120.300-k</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>2200.86</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4085-191-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.130.600-3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>10353</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3756-258-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.110.600-4</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>NETSUS SPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>11614.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3874-67-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.100.400-7</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>2523.99</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4134-274-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>69.110.200-9</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I. Municipalidad Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>22175.65</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>840405-21-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.110.700-0</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RIO CLARO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>10644.31</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2294-724-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>2747.47</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>5056-1527-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.606.901-2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>221607.75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2292-6734-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>76195.53</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2445-2218-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>4860.09</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3442-276-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.100.700-6</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>26610.78</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2318-537-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.130.100-1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>40280.79</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3251-468-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.252.700-3</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Intercity S.A.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
         <v>13733.65</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3300-99-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.100.500-3</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>7096.21</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2292-6894-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>2747.01</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>872535-246-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.100.300-0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TENO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>49233.63</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>840405-15-CM25</t>
+          <t>906973-9-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.110.700-0</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO CLARO</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10652.88</v>
+        <v>26632.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>906973-9-CM25</t>
+          <t>840405-15-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>69.110.700-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>I MUNICIPALIDAD DE RIO CLARO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>26632.2</v>
+        <v>10652.88</v>
       </c>
     </row>
     <row r="10">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3624,6 +3624,372 @@
       </c>
       <c r="M52" s="2" t="n">
         <v>49233.63</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3696-241-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.100.300-0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TENO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>8923.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3880-448-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.110.900-3</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>26610.78</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3876-176-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.100.400-7</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>6247.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3756-648-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.110.600-4</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>10335.15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3695-420-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.100.300-0</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TENO</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>923.13</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4401-826-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>49930.02</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1063,22 +1099,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3756-273-CM25</t>
+          <t>5056-960-SE25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1124,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,28 +1139,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>96.899.890-0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>12138</v>
+        <v>688920.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2294-658-CM25</t>
+          <t>3756-273-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,22 +1179,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,28 +1204,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2326.62</v>
+        <v>12138</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2292-708-CM25</t>
+          <t>2294-658-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1239,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1233,20 +1277,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3595.68</v>
+        <v>2326.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2292-788-CM25</t>
+          <t>2292-708-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1309,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1286,28 +1334,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35509.6</v>
+        <v>3595.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1142-220-CM25</t>
+          <t>2292-788-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1369,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.511.070-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,28 +1399,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6556.83</v>
+        <v>35509.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2318-690-CM25</t>
+          <t>1142-220-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1439,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1449,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>60.511.070-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,28 +1464,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2463.01</v>
+        <v>6556.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3876-125-CM25</t>
+          <t>2318-690-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1499,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1514,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,28 +1529,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3748.5</v>
+        <v>2463.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3300-124-CM25</t>
+          <t>3876-125-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1569,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1579,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1594,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1609,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6214.18</v>
+        <v>3748.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3880-423-CM25</t>
+          <t>3300-124-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1630,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1599,20 +1663,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>26632.2</v>
+        <v>6214.18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3756-627-CM25</t>
+          <t>3880-423-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1690,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,28 +1720,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>11584.65</v>
+        <v>26632.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2292-9091-CM25</t>
+          <t>3756-627-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1755,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,28 +1785,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2537.56</v>
+        <v>11584.65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2445-3581-CM25</t>
+          <t>2292-9091-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1825,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1835,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,28 +1850,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6247.5</v>
+        <v>2537.56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3231-464-CM25</t>
+          <t>2445-3581-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1885,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1915,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1930,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>14164.33</v>
+        <v>6247.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2827-927-CM25</t>
+          <t>3231-464-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1951,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1961,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1904,20 +1984,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4437.51</v>
+        <v>14164.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3696-477-CM25</t>
+          <t>2827-927-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +2016,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +2026,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,28 +2041,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3171.77</v>
+        <v>4437.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3876-242-CM25</t>
+          <t>3696-477-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +2076,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2091,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2026,20 +2114,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>954.38</v>
+        <v>3171.77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2445-1534-CM26</t>
+          <t>3876-242-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2141,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2156,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,28 +2171,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7076.45</v>
+        <v>954.38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2436-10-CM26</t>
+          <t>2445-1534-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,12 +2211,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2148,20 +2244,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>36561.68</v>
+        <v>7076.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1709-694-CM25</t>
+          <t>2436-10-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,22 +2276,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.120.400-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CAUQUENES</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2209,20 +2309,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>16559.9</v>
+        <v>36561.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2292-6077-CM26</t>
+          <t>1709-694-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,22 +2341,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.120.400-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CAUQUENES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,28 +2366,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2579.68</v>
+        <v>16559.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4401-124-CM26</t>
+          <t>2292-6077-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2401,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2416,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2331,20 +2439,24 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2875.98</v>
+        <v>2579.68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3876-16-CM26</t>
+          <t>4401-124-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,22 +2471,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,28 +2496,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2863.21</v>
+        <v>2875.98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3469-112-CM26</t>
+          <t>3876-16-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,22 +2536,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2561,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>28821.15</v>
+        <v>2863.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2291-351-CM26</t>
+          <t>3469-112-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2596,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,28 +2626,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4649.57</v>
+        <v>28821.15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4085-152-CM26</t>
+          <t>2291-351-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2666,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,28 +2691,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>12404.04</v>
+        <v>4649.57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1079566-96-CM26</t>
+          <t>4085-152-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,22 +2731,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,28 +2756,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1056.72</v>
+        <v>12404.04</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3470-18-CM26</t>
+          <t>1079566-96-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2796,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2806,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,28 +2821,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2200.86</v>
+        <v>1056.72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4085-191-CM26</t>
+          <t>3470-18-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,22 +2861,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2886,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2901,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10353</v>
+        <v>2200.86</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3756-258-CM26</t>
+          <t>4085-191-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2917,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,28 +2947,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>11614.4</v>
+        <v>10353</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3874-67-CM26</t>
+          <t>3756-258-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2987,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2997,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,28 +3012,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2523.99</v>
+        <v>11614.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4134-274-CM26</t>
+          <t>3874-67-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +3052,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +3062,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +3077,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +3092,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>22175.65</v>
+        <v>2523.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>840405-21-CM26</t>
+          <t>4134-274-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,27 +3108,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.110.700-0</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO CLARO</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3002,20 +3146,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>10644.31</v>
+        <v>22175.65</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2294-724-CM26</t>
+          <t>840405-21-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3173,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3188,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.700-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE RIO CLARO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,28 +3203,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2747.47</v>
+        <v>10644.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5056-1527-CM26</t>
+          <t>2294-724-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,27 +3238,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3268,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3135,13 +3287,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>221607.75</v>
+        <v>2747.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2292-6734-CM26</t>
+          <t>5056-1527-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,22 +3308,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3181,28 +3333,32 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>76195.53</v>
+        <v>221607.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2445-2218-CM26</t>
+          <t>2292-6734-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3217,22 +3373,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3242,28 +3398,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4860.09</v>
+        <v>76195.53</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3442-276-CM26</t>
+          <t>2445-2218-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3278,7 +3438,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3288,12 +3448,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3303,28 +3463,32 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>26610.78</v>
+        <v>4860.09</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2318-537-CM26</t>
+          <t>3442-276-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3339,7 +3503,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3349,12 +3513,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3372,20 +3536,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>40280.79</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3251-468-CM26</t>
+          <t>2318-537-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3400,22 +3568,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3425,28 +3593,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>13733.65</v>
+        <v>40280.79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3300-99-CM26</t>
+          <t>3251-468-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3456,27 +3628,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3486,28 +3658,32 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7096.21</v>
+        <v>13733.65</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2292-6894-CM26</t>
+          <t>3300-99-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3522,22 +3698,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3547,28 +3723,32 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2747.01</v>
+        <v>7096.21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>872535-246-CM26</t>
+          <t>2292-6894-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3583,22 +3763,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3608,28 +3788,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>49233.63</v>
+        <v>2747.01</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3696-241-CM26</t>
+          <t>872535-246-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3639,17 +3823,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3677,20 +3861,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>8923.6</v>
+        <v>49233.63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3880-448-CM26</t>
+          <t>3696-241-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3715,12 +3903,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3738,20 +3926,24 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>26610.78</v>
+        <v>8923.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3876-176-CM26</t>
+          <t>3880-448-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3776,12 +3968,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3791,28 +3983,32 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6247.5</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3756-648-CM26</t>
+          <t>3876-176-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,7 +4023,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,12 +4033,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +4048,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +4063,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>10335.15</v>
+        <v>6247.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3695-420-CM26</t>
+          <t>3756-648-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3888,22 +4084,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,82 +4109,151 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>923.13</v>
+        <v>10335.15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>3695-420-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.100.300-0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TENO</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>923.13</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>4401-826-CM26</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>69.110.500-8</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>76.854.651-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="n">
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
         <v>49930.02</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -904,7 +904,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>906973-9-CM25</t>
+          <t>840405-15-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>69.110.700-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>I MUNICIPALIDAD DE RIO CLARO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>26632.2</v>
+        <v>10652.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>840405-15-CM25</t>
+          <t>906973-9-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.110.700-0</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO CLARO</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10652.88</v>
+        <v>26632.2</v>
       </c>
     </row>
     <row r="10">
@@ -3878,7 +3878,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3696-241-CM26</t>
+          <t>3880-448-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3937,13 +3937,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8923.6</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3880-448-CM26</t>
+          <t>3696-241-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>26610.78</v>
+        <v>8923.6</v>
       </c>
     </row>
     <row r="56">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4255,6 +4255,132 @@
       </c>
       <c r="M59" s="2" t="n">
         <v>49930.02</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2445-2487-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2132-339-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>1431.53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/maule.xlsx
@@ -2606,7 +2606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
